--- a/output/Portfolio_Report.xlsx
+++ b/output/Portfolio_Report.xlsx
@@ -532,7 +532,7 @@
         <v>3.65</v>
       </c>
       <c r="H2" t="n">
-        <v>28.9</v>
+        <v>3816.582914572864</v>
       </c>
       <c r="I2" t="n">
         <v>8.710000000000001</v>
@@ -574,7 +574,7 @@
         <v>8.970000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>31.8</v>
+        <v>29.78800671841663</v>
       </c>
       <c r="I3" t="n">
         <v>13.2</v>
@@ -586,7 +586,7 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="4">
@@ -616,7 +616,7 @@
         <v>3.24</v>
       </c>
       <c r="H4" t="n">
-        <v>29.47</v>
+        <v>27.85107439569436</v>
       </c>
       <c r="I4" t="n">
         <v>7.95</v>
@@ -628,7 +628,7 @@
         <v>4.26</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>91.51000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -658,7 +658,7 @@
         <v>2.48</v>
       </c>
       <c r="H5" t="n">
-        <v>10.49</v>
+        <v>77.66510140873214</v>
       </c>
       <c r="I5" t="n">
         <v>10.34</v>
@@ -670,7 +670,7 @@
         <v>1.26</v>
       </c>
       <c r="L5" t="n">
-        <v>56.64</v>
+        <v>88.09</v>
       </c>
     </row>
     <row r="6">
@@ -700,7 +700,7 @@
         <v>6.08</v>
       </c>
       <c r="H6" t="n">
-        <v>0.52</v>
+        <v>50.94431367348518</v>
       </c>
       <c r="I6" t="n">
         <v>10.46</v>
@@ -712,7 +712,7 @@
         <v>1.62</v>
       </c>
       <c r="L6" t="n">
-        <v>58.91</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.24</v>
+        <v>800.5700000000001</v>
       </c>
     </row>
     <row r="5">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>83.11</v>
+        <v>91.29000000000001</v>
       </c>
     </row>
   </sheetData>
